--- a/esyluban/examples/dev/DataTables/common/全局常量配置表.xlsx
+++ b/esyluban/examples/dev/DataTables/common/全局常量配置表.xlsx
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>full_name="common.TbGlobalConfig" &amp; value_type="common.GlobalConfig" &amp; mode="one" &amp; read_schema_from_file="false" &amp; input="common/全局常量配置表.xlsx" &amp; output="common_tbglobalconfig"</t>
+          <t>full_name="common.TbGlobalConfig" &amp; mode="one" &amp; input="common/全局常量配置表.xlsx"</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
@@ -1066,7 +1066,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
